--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063F9AE6-EAF6-4743-9B10-11C0D06A0D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71770AC4-AF77-489F-A227-C13716C5CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -575,6 +575,9 @@
   </si>
   <si>
     <t>Chrüterenboden Pt. 1912</t>
+  </si>
+  <si>
+    <t>Bäregg</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C184"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2855,6 +2858,14 @@
         <v>1912</v>
       </c>
     </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>185</v>
+      </c>
+      <c r="C184">
+        <v>1688</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C150">
     <sortCondition ref="A2:A150"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71770AC4-AF77-489F-A227-C13716C5CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D9A9FE-352E-4041-8B40-4B0C59C30AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="4140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t>Bäregg</t>
+  </si>
+  <si>
+    <t>Mittler Tierberg</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2866,6 +2869,14 @@
         <v>1688</v>
       </c>
     </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>186</v>
+      </c>
+      <c r="C185">
+        <v>3309</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C150">
     <sortCondition ref="A2:A150"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D9A9FE-352E-4041-8B40-4B0C59C30AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE84CF07-F172-445A-A006-393D1BE0638C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="4140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -581,6 +581,9 @@
   </si>
   <si>
     <t>Mittler Tierberg</t>
+  </si>
+  <si>
+    <t>Obertal Pt 2717</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -1450,1436 +1453,1444 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>164</v>
       </c>
       <c r="C7">
-        <v>615</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>602</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9">
-        <v>1531</v>
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="C10">
-        <v>1757</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>600</v>
+        <v>122</v>
+      </c>
+      <c r="B11">
+        <v>1531</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>2136</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13">
-        <v>2690</v>
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14">
-        <v>2640</v>
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>2136</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="B15">
-        <v>2640</v>
-      </c>
-      <c r="C15">
-        <v>1057</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="B16">
-        <v>590</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2640</v>
       </c>
       <c r="C17">
-        <v>2401</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="B18">
-        <v>983</v>
+        <v>590</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19">
-        <v>2094</v>
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>2401</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20">
-        <v>792</v>
+        <v>125</v>
+      </c>
+      <c r="B20">
+        <v>983</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21">
-        <v>1420</v>
+        <v>185</v>
+      </c>
+      <c r="C21">
+        <v>1688</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22">
-        <v>1453</v>
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>2094</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="C23">
-        <v>1406</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>106</v>
+      <c r="A24" t="s">
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>1141</v>
+        <v>792</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25">
-        <v>491</v>
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>1420</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>139</v>
+      <c r="A26" t="s">
+        <v>14</v>
       </c>
       <c r="C26">
-        <v>3089</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="C27">
-        <v>567</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>2348</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29">
-        <v>574</v>
+      <c r="A29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29">
+        <v>1141</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>1430</v>
+        <v>491</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>20</v>
+      <c r="A31" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="C31">
-        <v>1426</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="C32">
-        <v>280</v>
+        <v>567</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="C33">
-        <v>1850</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34">
-        <v>1041</v>
+        <v>128</v>
+      </c>
+      <c r="B34">
+        <v>574</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35">
-        <v>1640</v>
+        <v>163</v>
+      </c>
+      <c r="C35">
+        <v>3030</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C36">
-        <v>620</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="C37">
-        <v>787</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>120</v>
+      <c r="A38" t="s">
+        <v>179</v>
       </c>
       <c r="C38">
-        <v>2993</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="C39">
-        <v>582</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C40">
-        <v>1205</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="C41">
-        <v>3087</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
       <c r="C42">
-        <v>2204</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="C43">
-        <v>2129</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C44">
-        <v>2412</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C45">
-        <v>760</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C46">
-        <v>1702</v>
+        <v>868</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47">
-        <v>2036</v>
+        <v>22</v>
+      </c>
+      <c r="B47">
+        <v>1640</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C48">
-        <v>2859</v>
+        <v>620</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C49">
-        <v>3075</v>
+        <v>787</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>123</v>
+      <c r="A50" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C50">
-        <v>2164</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C51">
-        <v>2098</v>
+        <v>582</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="C52">
-        <v>2171</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>36</v>
+      <c r="A53" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="C53">
-        <v>2391</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C54">
-        <v>1962</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="C55">
-        <v>1302</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C56">
-        <v>2580</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="C57">
-        <v>2005</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C58">
-        <v>1593</v>
+      <c r="A58" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58">
+        <v>866</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>136</v>
+      <c r="A59" t="s">
+        <v>126</v>
       </c>
       <c r="C59">
-        <v>1054</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60">
-        <v>1020</v>
+        <v>30</v>
+      </c>
+      <c r="C60">
+        <v>760</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="C61">
-        <v>3420</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C62">
-        <v>1067</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C63">
-        <v>1302</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64">
-        <v>1400</v>
+        <v>33</v>
+      </c>
+      <c r="C64">
+        <v>2859</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65">
-        <v>1327</v>
+        <v>173</v>
+      </c>
+      <c r="C65">
+        <v>1082</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66">
-        <v>1305</v>
+        <v>34</v>
+      </c>
+      <c r="C66">
+        <v>3075</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>47</v>
+        <v>177</v>
+      </c>
+      <c r="C67">
+        <v>2795</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68">
-        <v>1256</v>
+        <v>166</v>
+      </c>
+      <c r="C68">
+        <v>1409</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69">
-        <v>2440</v>
+      <c r="A69" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69">
+        <v>2164</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B70">
-        <v>1052</v>
+      <c r="A70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70">
+        <v>2098</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>48</v>
-      </c>
-      <c r="B71">
-        <v>2164</v>
+        <v>144</v>
+      </c>
+      <c r="C71">
+        <v>2171</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C72">
-        <v>1548</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C73">
-        <v>1948</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C74">
-        <v>3035</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C75">
-        <v>2594</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>52</v>
-      </c>
-      <c r="B76">
-        <v>280</v>
+        <v>39</v>
+      </c>
+      <c r="C76">
+        <v>2580</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="C77">
-        <v>1827</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>54</v>
-      </c>
-      <c r="B78">
-        <v>565</v>
+        <v>40</v>
+      </c>
+      <c r="C78">
+        <v>1593</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>55</v>
+      <c r="A79" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="C79">
-        <v>1597</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>56</v>
-      </c>
-      <c r="C80">
-        <v>673</v>
+        <v>41</v>
+      </c>
+      <c r="B80">
+        <v>1020</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="C81">
-        <v>797</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C82">
-        <v>1707</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="C83">
-        <v>2923</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B84">
-        <v>2200</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>60</v>
-      </c>
-      <c r="C85">
-        <v>600</v>
+        <v>45</v>
+      </c>
+      <c r="B85">
+        <v>1327</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>61</v>
-      </c>
-      <c r="C86">
-        <v>691</v>
+        <v>46</v>
+      </c>
+      <c r="B86">
+        <v>1305</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>62</v>
-      </c>
-      <c r="B87">
-        <v>925</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>63</v>
-      </c>
-      <c r="C88">
-        <v>1020</v>
+        <v>141</v>
+      </c>
+      <c r="B88">
+        <v>1256</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="C89">
-        <v>2362</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>65</v>
-      </c>
-      <c r="C90">
-        <v>691</v>
+      <c r="A90" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90">
+        <v>2440</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>171</v>
-      </c>
-      <c r="C91">
-        <v>2362</v>
+      <c r="A91" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91">
+        <v>1052</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>130</v>
-      </c>
-      <c r="C92">
-        <v>1677</v>
+        <v>48</v>
+      </c>
+      <c r="B92">
+        <v>2164</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="C93">
-        <v>1950</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="C94">
-        <v>1208</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C95">
-        <v>2989</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>68</v>
-      </c>
-      <c r="B96">
-        <v>1849</v>
+        <v>51</v>
+      </c>
+      <c r="C96">
+        <v>2594</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>127</v>
-      </c>
-      <c r="C97">
-        <v>2949</v>
+        <v>52</v>
+      </c>
+      <c r="B97">
+        <v>280</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>182</v>
       </c>
       <c r="C98">
-        <v>1628</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C99">
-        <v>1863</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="2" t="s">
-        <v>115</v>
+      <c r="A100" t="s">
+        <v>168</v>
       </c>
       <c r="C100">
-        <v>1358</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>140</v>
-      </c>
-      <c r="C101">
-        <v>1341</v>
+        <v>54</v>
+      </c>
+      <c r="B101">
+        <v>565</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C102">
-        <v>2245</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="C103">
-        <v>3259</v>
+        <v>673</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C104">
-        <v>1769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="C105">
-        <v>2323</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C106">
-        <v>1052</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C107">
-        <v>1065</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>73</v>
-      </c>
-      <c r="C108">
-        <v>1050</v>
+        <v>59</v>
+      </c>
+      <c r="B108">
+        <v>2200</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="C109">
-        <v>1409</v>
+        <v>600</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
-        <v>105</v>
+      <c r="A110" t="s">
+        <v>155</v>
+      </c>
+      <c r="C110">
+        <v>976</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="C111">
-        <v>2969</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>75</v>
-      </c>
-      <c r="B112">
-        <v>1937</v>
+        <v>158</v>
+      </c>
+      <c r="C112">
+        <v>2883</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>76</v>
-      </c>
-      <c r="B113">
-        <v>1037</v>
+        <v>61</v>
+      </c>
+      <c r="C113">
+        <v>691</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>77</v>
-      </c>
-      <c r="C114">
-        <v>2927</v>
+        <v>62</v>
+      </c>
+      <c r="B114">
+        <v>925</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>78</v>
-      </c>
-      <c r="B115">
-        <v>1455</v>
+        <v>63</v>
+      </c>
+      <c r="C115">
+        <v>1020</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="C116">
-        <v>1224</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="C117">
-        <v>1359</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C118">
-        <v>2069</v>
+        <v>691</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>80</v>
-      </c>
-      <c r="B119">
-        <v>800</v>
+        <v>130</v>
+      </c>
+      <c r="C119">
+        <v>1677</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>81</v>
-      </c>
-      <c r="B120">
-        <v>2051</v>
+        <v>149</v>
+      </c>
+      <c r="C120">
+        <v>1950</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="C121">
-        <v>1105</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C122">
-        <v>3020</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="2" t="s">
-        <v>131</v>
+      <c r="A123" t="s">
+        <v>67</v>
       </c>
       <c r="C123">
-        <v>1370</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="C124">
-        <v>1677</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B125">
-        <v>1439</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="C126">
-        <v>1863</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C127">
-        <v>3502</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C128">
-        <v>2855</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>87</v>
-      </c>
-      <c r="B129">
-        <v>1750</v>
+      <c r="A129" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C129">
+        <v>1358</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="C130">
-        <v>2326</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C131">
-        <v>1328</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C132">
-        <v>2798</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="C133">
-        <v>2911</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="C134">
-        <v>1851</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>92</v>
-      </c>
-      <c r="B135">
-        <v>1346</v>
+        <v>108</v>
+      </c>
+      <c r="C135">
+        <v>1052</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C136">
-        <v>1649</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C137">
-        <v>1822</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="C138">
-        <v>2303</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C139">
-        <v>2705</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="C140">
-        <v>1217</v>
+        <v>618</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>135</v>
-      </c>
-      <c r="C141">
-        <v>1945</v>
+      <c r="A141" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C142">
-        <v>3690</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>95</v>
-      </c>
-      <c r="C143">
-        <v>2891</v>
+        <v>75</v>
+      </c>
+      <c r="B143">
+        <v>1937</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>96</v>
+      <c r="A144" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C144">
-        <v>3244</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>97</v>
-      </c>
-      <c r="B145">
-        <v>1400</v>
+        <v>169</v>
+      </c>
+      <c r="C145">
+        <v>1617</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C146">
-        <v>2005</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>99</v>
-      </c>
-      <c r="C147">
-        <v>1875</v>
+        <v>76</v>
+      </c>
+      <c r="B147">
+        <v>1037</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C148">
-        <v>1390</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C149">
-        <v>1079</v>
+      <c r="A149" t="s">
+        <v>78</v>
+      </c>
+      <c r="B149">
+        <v>1455</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="C150">
-        <v>976</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="C151">
-        <v>2658</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="C152">
-        <v>2090</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C153">
-        <v>2517</v>
+      <c r="A153" t="s">
+        <v>80</v>
+      </c>
+      <c r="B153">
+        <v>800</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>153</v>
-      </c>
-      <c r="C154">
-        <v>618</v>
+        <v>81</v>
+      </c>
+      <c r="B154">
+        <v>2051</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="C155">
-        <v>1013</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="C156">
-        <v>976</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>156</v>
+      <c r="A157" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="C157">
-        <v>1540</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="C158">
-        <v>1223</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>158</v>
-      </c>
-      <c r="C159">
-        <v>2883</v>
+        <v>113</v>
+      </c>
+      <c r="B159">
+        <v>1439</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="C160">
-        <v>4634</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C161">
-        <v>1706</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="C162">
-        <v>3586</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="C163">
-        <v>2269</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>163</v>
-      </c>
-      <c r="C164">
-        <v>3030</v>
+        <v>87</v>
+      </c>
+      <c r="B164">
+        <v>1750</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="C165">
-        <v>4027</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="C166">
-        <v>1562</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C167">
-        <v>1409</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>167</v>
+        <v>90</v>
       </c>
       <c r="C168">
-        <v>2835</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="C169">
-        <v>1171</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="C170">
-        <v>1617</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A171" s="2" t="s">
-        <v>170</v>
+      <c r="A171" t="s">
+        <v>92</v>
       </c>
       <c r="B171">
-        <v>866</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="C172">
-        <v>1617</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="C173">
-        <v>1082</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="C174">
-        <v>1707</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="C175">
-        <v>868</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" s="2" t="s">
-        <v>176</v>
+      <c r="A176" t="s">
+        <v>119</v>
       </c>
       <c r="C176">
-        <v>1196</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="C177">
-        <v>2795</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="C178">
-        <v>1932</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="C179">
-        <v>1648</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="C180">
-        <v>1574</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>181</v>
-      </c>
-      <c r="C181">
-        <v>1901</v>
+        <v>97</v>
+      </c>
+      <c r="B181">
+        <v>1400</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="C182">
-        <v>1860</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="C183">
-        <v>1912</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="C184">
-        <v>1688</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>186</v>
+      <c r="A185" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="C185">
-        <v>3309</v>
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>101</v>
+      </c>
+      <c r="C186">
+        <v>976</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C150">
-    <sortCondition ref="A2:A150"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
+    <sortCondition ref="A2:A186"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE84CF07-F172-445A-A006-393D1BE0638C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687AB438-2BE0-4F84-AD5A-73FF8A19E551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>Obertal Pt 2717</t>
+  </si>
+  <si>
+    <t>Moosbielen Wegweiser</t>
   </si>
 </sst>
 </file>
@@ -1396,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2888,6 +2891,14 @@
         <v>976</v>
       </c>
     </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>188</v>
+      </c>
+      <c r="C187">
+        <v>1670</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687AB438-2BE0-4F84-AD5A-73FF8A19E551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041EA152-386F-422D-B939-FA9CDFDBCD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -587,6 +587,9 @@
   </si>
   <si>
     <t>Moosbielen Wegweiser</t>
+  </si>
+  <si>
+    <t>Taellihuette</t>
   </si>
 </sst>
 </file>
@@ -1399,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C188"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2899,6 +2902,14 @@
         <v>1670</v>
       </c>
     </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>189</v>
+      </c>
+      <c r="C188">
+        <v>1727</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041EA152-386F-422D-B939-FA9CDFDBCD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34766B9-010F-44E8-86E0-1CD144EEB371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t>Taellihuette</t>
+  </si>
+  <si>
+    <t>Irtschelen</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2910,6 +2913,14 @@
         <v>1727</v>
       </c>
     </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>190</v>
+      </c>
+      <c r="C189">
+        <v>1600</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34766B9-010F-44E8-86E0-1CD144EEB371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC31C2-68BE-4ECE-9E1F-B936EA5F08BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -593,6 +593,12 @@
   </si>
   <si>
     <t>Irtschelen</t>
+  </si>
+  <si>
+    <t>Lungern Talstation Turren</t>
+  </si>
+  <si>
+    <t>Lungern Schoenbuehl</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C191"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2921,6 +2927,22 @@
         <v>1600</v>
       </c>
     </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>191</v>
+      </c>
+      <c r="C190">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>192</v>
+      </c>
+      <c r="C191">
+        <v>2011</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC31C2-68BE-4ECE-9E1F-B936EA5F08BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC09A7D-6F51-419B-9255-53A1925EEB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -599,6 +599,9 @@
   </si>
   <si>
     <t>Lungern Schoenbuehl</t>
+  </si>
+  <si>
+    <t>Tannalp</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C191"/>
+  <dimension ref="A1:C192"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2943,6 +2946,14 @@
         <v>2011</v>
       </c>
     </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>193</v>
+      </c>
+      <c r="C192">
+        <v>1974</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC09A7D-6F51-419B-9255-53A1925EEB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91AA628-40F1-4111-9586-6059E32C4534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>Tannalp</t>
+  </si>
+  <si>
+    <t>Gadmen Lodge</t>
   </si>
 </sst>
 </file>
@@ -1414,14 +1417,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C192"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C193"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -1432,7 +1435,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -1440,12 +1443,12 @@
         <v>596</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1461,7 +1464,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1469,7 +1472,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>164</v>
       </c>
@@ -1477,7 +1480,7 @@
         <v>4027</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1496,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>156</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>122</v>
       </c>
@@ -1509,7 +1512,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1525,7 +1528,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1533,7 +1536,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>117</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1560,7 +1563,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1568,7 +1571,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>185</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>162</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1624,7 +1627,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>167</v>
       </c>
@@ -1640,7 +1643,7 @@
         <v>2835</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>106</v>
       </c>
@@ -1656,7 +1659,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1664,7 +1667,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>139</v>
       </c>
@@ -1672,7 +1675,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1680,7 +1683,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -1696,7 +1699,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>163</v>
       </c>
@@ -1704,7 +1707,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -1712,7 +1715,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>154</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>179</v>
       </c>
@@ -1728,7 +1731,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -1736,7 +1739,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -1752,7 +1755,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>159</v>
       </c>
@@ -1760,7 +1763,7 @@
         <v>4634</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>181</v>
       </c>
@@ -1768,7 +1771,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>147</v>
       </c>
@@ -1776,7 +1779,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>175</v>
       </c>
@@ -1792,7 +1795,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -1816,7 +1819,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>120</v>
       </c>
@@ -1824,7 +1827,7 @@
         <v>2993</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -1832,7 +1835,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -1840,7 +1843,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>176</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>3087</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -1864,7 +1867,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -1872,7 +1875,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>170</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>126</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>30</v>
       </c>
@@ -1904,7 +1907,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -1912,7 +1915,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -1920,7 +1923,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -1936,7 +1939,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>173</v>
       </c>
@@ -1944,7 +1947,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>34</v>
       </c>
@@ -1952,7 +1955,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>177</v>
       </c>
@@ -1960,7 +1963,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>166</v>
       </c>
@@ -1968,7 +1971,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>123</v>
       </c>
@@ -1976,7 +1979,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>35</v>
       </c>
@@ -1984,7 +1987,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>144</v>
       </c>
@@ -1992,7 +1995,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>36</v>
       </c>
@@ -2000,7 +2003,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>180</v>
       </c>
@@ -2008,7 +2011,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -2016,7 +2019,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>38</v>
       </c>
@@ -2024,7 +2027,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>111</v>
       </c>
@@ -2040,7 +2043,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -2048,7 +2051,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>136</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>41</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>121</v>
       </c>
@@ -2072,7 +2075,7 @@
         <v>3420</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>42</v>
       </c>
@@ -2080,7 +2083,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>43</v>
       </c>
@@ -2088,7 +2091,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -2096,7 +2099,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>45</v>
       </c>
@@ -2104,7 +2107,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>46</v>
       </c>
@@ -2112,12 +2115,12 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>141</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>160</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>112</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>183</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>48</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>49</v>
       </c>
@@ -2165,7 +2168,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>148</v>
       </c>
@@ -2173,7 +2176,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>50</v>
       </c>
@@ -2181,7 +2184,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>51</v>
       </c>
@@ -2189,7 +2192,7 @@
         <v>2594</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>52</v>
       </c>
@@ -2197,7 +2200,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>182</v>
       </c>
@@ -2205,7 +2208,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -2213,7 +2216,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>168</v>
       </c>
@@ -2221,7 +2224,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>54</v>
       </c>
@@ -2229,7 +2232,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>55</v>
       </c>
@@ -2237,7 +2240,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>56</v>
       </c>
@@ -2245,7 +2248,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>57</v>
       </c>
@@ -2253,7 +2256,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>58</v>
       </c>
@@ -2261,7 +2264,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>174</v>
       </c>
@@ -2269,7 +2272,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>137</v>
       </c>
@@ -2277,7 +2280,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>59</v>
       </c>
@@ -2285,7 +2288,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>60</v>
       </c>
@@ -2293,7 +2296,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2301,7 +2304,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>186</v>
       </c>
@@ -2309,7 +2312,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>158</v>
       </c>
@@ -2317,7 +2320,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>61</v>
       </c>
@@ -2325,7 +2328,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>62</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>63</v>
       </c>
@@ -2341,7 +2344,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>64</v>
       </c>
@@ -2349,7 +2352,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>171</v>
       </c>
@@ -2357,7 +2360,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>65</v>
       </c>
@@ -2365,7 +2368,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -2373,7 +2376,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>149</v>
       </c>
@@ -2381,7 +2384,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>151</v>
       </c>
@@ -2389,7 +2392,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -2397,7 +2400,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>67</v>
       </c>
@@ -2405,7 +2408,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>187</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>68</v>
       </c>
@@ -2421,7 +2424,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -2429,7 +2432,7 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>69</v>
       </c>
@@ -2437,7 +2440,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -2445,7 +2448,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>115</v>
       </c>
@@ -2453,7 +2456,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -2461,7 +2464,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>71</v>
       </c>
@@ -2469,7 +2472,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>116</v>
       </c>
@@ -2477,7 +2480,7 @@
         <v>3259</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>72</v>
       </c>
@@ -2485,7 +2488,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>146</v>
       </c>
@@ -2493,7 +2496,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -2501,7 +2504,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>109</v>
       </c>
@@ -2509,7 +2512,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>73</v>
       </c>
@@ -2517,7 +2520,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>143</v>
       </c>
@@ -2525,7 +2528,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>157</v>
       </c>
@@ -2533,7 +2536,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>153</v>
       </c>
@@ -2541,12 +2544,12 @@
         <v>618</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>74</v>
       </c>
@@ -2554,7 +2557,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>75</v>
       </c>
@@ -2562,7 +2565,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>152</v>
       </c>
@@ -2570,7 +2573,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>169</v>
       </c>
@@ -2578,7 +2581,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>172</v>
       </c>
@@ -2586,7 +2589,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>76</v>
       </c>
@@ -2594,7 +2597,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>77</v>
       </c>
@@ -2602,7 +2605,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>78</v>
       </c>
@@ -2610,7 +2613,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>145</v>
       </c>
@@ -2618,7 +2621,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>124</v>
       </c>
@@ -2626,7 +2629,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>79</v>
       </c>
@@ -2634,7 +2637,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>80</v>
       </c>
@@ -2642,7 +2645,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>81</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>82</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>83</v>
       </c>
@@ -2666,7 +2669,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>131</v>
       </c>
@@ -2674,7 +2677,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>110</v>
       </c>
@@ -2682,7 +2685,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>113</v>
       </c>
@@ -2690,7 +2693,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>84</v>
       </c>
@@ -2698,7 +2701,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>178</v>
       </c>
@@ -2706,7 +2709,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>85</v>
       </c>
@@ -2714,7 +2717,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>86</v>
       </c>
@@ -2722,7 +2725,7 @@
         <v>2855</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>87</v>
       </c>
@@ -2730,7 +2733,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>88</v>
       </c>
@@ -2738,7 +2741,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>89</v>
       </c>
@@ -2746,7 +2749,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>165</v>
       </c>
@@ -2754,7 +2757,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>90</v>
       </c>
@@ -2762,7 +2765,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>134</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>2911</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>91</v>
       </c>
@@ -2778,7 +2781,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>92</v>
       </c>
@@ -2786,7 +2789,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>93</v>
       </c>
@@ -2794,7 +2797,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>94</v>
       </c>
@@ -2802,7 +2805,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>107</v>
       </c>
@@ -2810,7 +2813,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>133</v>
       </c>
@@ -2818,7 +2821,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>119</v>
       </c>
@@ -2826,7 +2829,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>135</v>
       </c>
@@ -2834,7 +2837,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>114</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>95</v>
       </c>
@@ -2850,7 +2853,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>96</v>
       </c>
@@ -2858,7 +2861,7 @@
         <v>3244</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>97</v>
       </c>
@@ -2866,7 +2869,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>98</v>
       </c>
@@ -2874,7 +2877,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>99</v>
       </c>
@@ -2882,7 +2885,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>100</v>
       </c>
@@ -2890,7 +2893,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>129</v>
       </c>
@@ -2898,7 +2901,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>101</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>188</v>
       </c>
@@ -2914,7 +2917,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>189</v>
       </c>
@@ -2922,7 +2925,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -2930,7 +2933,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>191</v>
       </c>
@@ -2938,7 +2941,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>192</v>
       </c>
@@ -2946,12 +2949,20 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>193</v>
       </c>
       <c r="C192">
         <v>1974</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>194</v>
+      </c>
+      <c r="C193">
+        <v>1205</v>
       </c>
     </row>
   </sheetData>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91AA628-40F1-4111-9586-6059E32C4534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4D0643-27EA-477A-80FB-676647C4BA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>Gadmen Lodge</t>
+  </si>
+  <si>
+    <t>Tierberglihuette</t>
   </si>
 </sst>
 </file>
@@ -1417,14 +1420,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C193"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C194"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -1443,12 +1446,12 @@
         <v>596</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1464,7 +1467,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>164</v>
       </c>
@@ -1480,7 +1483,7 @@
         <v>4027</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1488,7 +1491,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1496,7 +1499,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>156</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>122</v>
       </c>
@@ -1512,7 +1515,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1520,7 +1523,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1528,7 +1531,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1536,7 +1539,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>117</v>
       </c>
@@ -1544,7 +1547,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -1552,7 +1555,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1563,7 +1566,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1571,7 +1574,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1579,7 +1582,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>185</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>162</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1619,7 +1622,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>167</v>
       </c>
@@ -1643,7 +1646,7 @@
         <v>2835</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1651,7 +1654,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>106</v>
       </c>
@@ -1659,7 +1662,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1667,7 +1670,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>139</v>
       </c>
@@ -1675,7 +1678,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1683,7 +1686,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1691,7 +1694,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>163</v>
       </c>
@@ -1707,7 +1710,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -1715,7 +1718,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>154</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>179</v>
       </c>
@@ -1731,7 +1734,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1747,7 +1750,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -1755,7 +1758,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>159</v>
       </c>
@@ -1763,7 +1766,7 @@
         <v>4634</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>181</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>147</v>
       </c>
@@ -1779,7 +1782,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>175</v>
       </c>
@@ -1795,7 +1798,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1803,7 +1806,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -1811,7 +1814,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -1819,7 +1822,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>120</v>
       </c>
@@ -1827,7 +1830,7 @@
         <v>2993</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -1835,7 +1838,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -1843,7 +1846,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>176</v>
       </c>
@@ -1851,7 +1854,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>3087</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -1867,7 +1870,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -1875,7 +1878,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -1883,7 +1886,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>170</v>
       </c>
@@ -1891,7 +1894,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>126</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>30</v>
       </c>
@@ -1907,7 +1910,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -1915,7 +1918,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -1923,7 +1926,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -1931,7 +1934,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -1939,7 +1942,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>173</v>
       </c>
@@ -1947,7 +1950,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>34</v>
       </c>
@@ -1955,7 +1958,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>177</v>
       </c>
@@ -1963,7 +1966,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>166</v>
       </c>
@@ -1971,7 +1974,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>123</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>35</v>
       </c>
@@ -1987,7 +1990,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>144</v>
       </c>
@@ -1995,7 +1998,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>36</v>
       </c>
@@ -2003,7 +2006,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>180</v>
       </c>
@@ -2011,7 +2014,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -2019,7 +2022,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>38</v>
       </c>
@@ -2027,7 +2030,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -2035,7 +2038,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>111</v>
       </c>
@@ -2043,7 +2046,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -2051,7 +2054,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>136</v>
       </c>
@@ -2059,7 +2062,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>41</v>
       </c>
@@ -2067,7 +2070,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>121</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>3420</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>42</v>
       </c>
@@ -2083,7 +2086,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>43</v>
       </c>
@@ -2091,7 +2094,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -2099,7 +2102,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>45</v>
       </c>
@@ -2107,7 +2110,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>46</v>
       </c>
@@ -2115,12 +2118,12 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>141</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>160</v>
       </c>
@@ -2136,7 +2139,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>112</v>
       </c>
@@ -2144,7 +2147,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>183</v>
       </c>
@@ -2152,7 +2155,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>48</v>
       </c>
@@ -2160,7 +2163,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>49</v>
       </c>
@@ -2168,7 +2171,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>148</v>
       </c>
@@ -2176,7 +2179,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>50</v>
       </c>
@@ -2184,7 +2187,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>51</v>
       </c>
@@ -2192,7 +2195,7 @@
         <v>2594</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>52</v>
       </c>
@@ -2200,7 +2203,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>182</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>168</v>
       </c>
@@ -2224,7 +2227,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>54</v>
       </c>
@@ -2232,7 +2235,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>55</v>
       </c>
@@ -2240,7 +2243,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>56</v>
       </c>
@@ -2248,7 +2251,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>57</v>
       </c>
@@ -2256,7 +2259,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>58</v>
       </c>
@@ -2264,7 +2267,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>174</v>
       </c>
@@ -2272,7 +2275,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>137</v>
       </c>
@@ -2280,7 +2283,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>59</v>
       </c>
@@ -2288,7 +2291,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>60</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2304,7 +2307,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>186</v>
       </c>
@@ -2312,7 +2315,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>158</v>
       </c>
@@ -2320,7 +2323,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>61</v>
       </c>
@@ -2328,7 +2331,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>62</v>
       </c>
@@ -2336,7 +2339,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>63</v>
       </c>
@@ -2344,7 +2347,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>64</v>
       </c>
@@ -2352,7 +2355,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>171</v>
       </c>
@@ -2360,7 +2363,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>65</v>
       </c>
@@ -2368,7 +2371,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -2376,7 +2379,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>149</v>
       </c>
@@ -2384,7 +2387,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>151</v>
       </c>
@@ -2392,7 +2395,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -2400,7 +2403,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>67</v>
       </c>
@@ -2408,7 +2411,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>187</v>
       </c>
@@ -2416,7 +2419,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>68</v>
       </c>
@@ -2424,7 +2427,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -2432,7 +2435,7 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>69</v>
       </c>
@@ -2440,7 +2443,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>115</v>
       </c>
@@ -2456,7 +2459,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>71</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>116</v>
       </c>
@@ -2480,7 +2483,7 @@
         <v>3259</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>72</v>
       </c>
@@ -2488,7 +2491,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>146</v>
       </c>
@@ -2496,7 +2499,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>109</v>
       </c>
@@ -2512,7 +2515,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>73</v>
       </c>
@@ -2520,7 +2523,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>143</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>157</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>153</v>
       </c>
@@ -2544,12 +2547,12 @@
         <v>618</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>74</v>
       </c>
@@ -2557,7 +2560,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>75</v>
       </c>
@@ -2565,7 +2568,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>152</v>
       </c>
@@ -2573,7 +2576,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>169</v>
       </c>
@@ -2581,7 +2584,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>172</v>
       </c>
@@ -2589,7 +2592,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>76</v>
       </c>
@@ -2597,7 +2600,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>77</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>78</v>
       </c>
@@ -2613,7 +2616,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>145</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>124</v>
       </c>
@@ -2629,7 +2632,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>79</v>
       </c>
@@ -2637,7 +2640,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>80</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>81</v>
       </c>
@@ -2653,7 +2656,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>82</v>
       </c>
@@ -2661,7 +2664,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>83</v>
       </c>
@@ -2669,7 +2672,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>131</v>
       </c>
@@ -2677,7 +2680,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>110</v>
       </c>
@@ -2685,7 +2688,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>113</v>
       </c>
@@ -2693,7 +2696,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>84</v>
       </c>
@@ -2701,7 +2704,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>178</v>
       </c>
@@ -2709,7 +2712,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>85</v>
       </c>
@@ -2717,7 +2720,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>86</v>
       </c>
@@ -2725,7 +2728,7 @@
         <v>2855</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>87</v>
       </c>
@@ -2733,7 +2736,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>88</v>
       </c>
@@ -2741,7 +2744,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>89</v>
       </c>
@@ -2749,7 +2752,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>165</v>
       </c>
@@ -2757,7 +2760,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>90</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>134</v>
       </c>
@@ -2773,7 +2776,7 @@
         <v>2911</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>91</v>
       </c>
@@ -2781,7 +2784,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>92</v>
       </c>
@@ -2789,7 +2792,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>93</v>
       </c>
@@ -2797,7 +2800,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>94</v>
       </c>
@@ -2805,7 +2808,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>107</v>
       </c>
@@ -2813,7 +2816,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>133</v>
       </c>
@@ -2821,7 +2824,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>119</v>
       </c>
@@ -2829,7 +2832,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>135</v>
       </c>
@@ -2837,7 +2840,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>114</v>
       </c>
@@ -2845,7 +2848,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>95</v>
       </c>
@@ -2853,7 +2856,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>96</v>
       </c>
@@ -2861,7 +2864,7 @@
         <v>3244</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>97</v>
       </c>
@@ -2869,7 +2872,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>98</v>
       </c>
@@ -2877,7 +2880,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>99</v>
       </c>
@@ -2885,7 +2888,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>100</v>
       </c>
@@ -2893,7 +2896,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>129</v>
       </c>
@@ -2901,7 +2904,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>101</v>
       </c>
@@ -2909,7 +2912,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>188</v>
       </c>
@@ -2917,7 +2920,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>189</v>
       </c>
@@ -2925,7 +2928,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -2933,7 +2936,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>191</v>
       </c>
@@ -2941,7 +2944,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>192</v>
       </c>
@@ -2949,7 +2952,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>193</v>
       </c>
@@ -2957,12 +2960,20 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>194</v>
       </c>
       <c r="C193">
         <v>1205</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>195</v>
+      </c>
+      <c r="C194">
+        <v>2795</v>
       </c>
     </row>
   </sheetData>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4D0643-27EA-477A-80FB-676647C4BA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EE3357-B0D7-4E22-8C7E-4959E40C78CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -608,6 +608,12 @@
   </si>
   <si>
     <t>Tierberglihuette</t>
+  </si>
+  <si>
+    <t>Lauteraarhuette</t>
+  </si>
+  <si>
+    <t>Grimsel Hospiz</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C194"/>
+  <dimension ref="A1:C196"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2976,6 +2982,22 @@
         <v>2795</v>
       </c>
     </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>196</v>
+      </c>
+      <c r="C195">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>197</v>
+      </c>
+      <c r="C196">
+        <v>1980</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>
